--- a/docs/production_scheduling/CIP拓扑导入模板.xlsx
+++ b/docs/production_scheduling/CIP拓扑导入模板.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -548,19 +548,26 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>6) 带 * 的列必填(表头标黄)。下拉填错词会被拒。</t>
+          <t>5b) 清洗时序 + 单位:CIP/SIP 时长用「分钟」,DHT(脏停放=变脏后须几小时内开洗)/ CHT(洁净有效期=洗完几小时内须被用)用「小时」。只对要 CIP 的设备/管线填,免洗的留空。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>7) 填写顺序:先「站」「房间」→ 再「设备」→ 再「管线」。下游下拉来自上游已录的编码,自动增长。</t>
+          <t>6) 带 * 的列必填(表头标黄)。下拉填错词会被拒。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>7) 填写顺序:先「站」「房间」→ 再「设备」→ 再「管线」。下游下拉来自上游已录的编码,自动增长。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>8) 导入按「设施+编码」upsert:已存在则更新,不存在则新增;重复导入不会建重复。</t>
         </is>
@@ -785,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -796,7 +803,11 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -842,6 +853,26 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
+          <t>CIP时长(分钟)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>SIP时长(分钟)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>DHT(小时)</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>CHT(小时)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
@@ -879,7 +910,17 @@
           <t>CIP-1</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>组织留空=随房间</t>
         </is>
@@ -918,7 +959,23 @@
           <t>CIP-1</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>CIP后SIP</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -949,9 +1006,13 @@
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>一次性免CIP,不填站</t>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>一次性免CIP,站/时长全留空</t>
         </is>
       </c>
     </row>
@@ -988,7 +1049,17 @@
           <t>CIP-1</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>母系统:下面挂多个使用点</t>
         </is>
@@ -1023,7 +1094,11 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>子设备:房间/组织留空→随上级BUF-SYS</t>
         </is>
@@ -1062,10 +1137,20 @@
           <t>CIP-2</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="M7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="请从下拉中选择有效值" type="list" errorStyle="stop">
       <formula1>=设备类型</formula1>
     </dataValidation>
@@ -1083,6 +1168,9 @@
     </dataValidation>
     <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="仅清洗方式=CIP 时填,选「站」表里已录的站编码" type="list" errorStyle="warning">
       <formula1>=站编码</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1095,7 +1183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1103,7 +1191,10 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,6 +1225,21 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>CIP时长(分钟)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>DHT(小时)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>CHT(小时)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
@@ -1164,14 +1270,23 @@
           <t>CIP-1</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>示例行</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="选「设备」表里已录的设备编码" type="list" errorStyle="warning">
       <formula1>=设备编码</formula1>
     </dataValidation>
@@ -1180,6 +1295,9 @@
     </dataValidation>
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="选「站」表里已录的站编码" type="list" errorStyle="warning">
       <formula1>=站编码</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/production_scheduling/CIP拓扑导入模板.xlsx
+++ b/docs/production_scheduling/CIP拓扑导入模板.xlsx
@@ -19,7 +19,7 @@
     <definedName name="站编码">OFFSET('站'!$A$2,0,0,MAX(1,COUNTA('站'!$A$2:$A$1000)),1)</definedName>
     <definedName name="房间编码">OFFSET('房间'!$A$2,0,0,MAX(1,COUNTA('房间'!$A$2:$A$1000)),1)</definedName>
     <definedName name="设备编码">OFFSET('设备'!$A$2,0,0,MAX(1,COUNTA('设备'!$A$2:$A$1000)),1)</definedName>
-    <definedName name="设备类型">'选项'!$A$2:$A$7</definedName>
+    <definedName name="设备类型">'选项'!$A$2:$A$24</definedName>
     <definedName name="效期类别">'选项'!$B$2:$B$7</definedName>
     <definedName name="起算基准">'选项'!$C$2:$C$4</definedName>
     <definedName name="清洗方式">'选项'!$D$2:$D$5</definedName>
@@ -480,10 +480,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="108" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,47 +527,68 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4) 引用一律用「编码」:设备的 上级设备编码/房间编码←房间表、CIP站编码←站表;管线的 起点/终点设备编码←设备表、CIP站编码←站表。</t>
+          <t>3c) 「类型」取自系统「设备类型」字典(可在系统里随时增删改);本下拉为当前默认值、可直接改写,导入时以系统活字典校验(不在字典或已停用会被拒)。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5) 设备「清洗方式」:CIP(在线清洗,要填 CIP站)/ 一次性(免洗,如一次性反应器)/ COP(离线)/ 其他。</t>
+          <t>4) 引用一律用「编码」:设备的 上级设备编码/房间编码←房间表、CIP站编码←站表;管线的 起点/终点设备编码←设备表、CIP站编码←站表。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">     只有 CIP 设备才进 CIP 排程、才算尖峰;非 CIP 设备不填 CIP站。</t>
+          <t>5) 设备「清洗方式」:CIP(在线清洗,要填 CIP站)/ 一次性(免洗,如一次性反应器)/ COP(离线)/ 其他。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5b) 清洗时序 + 单位:CIP/SIP 时长用「分钟」,DHT(脏停放=变脏后须几小时内开洗)/ CHT(洁净有效期=洗完几小时内须被用)用「小时」。只对要 CIP 的设备/管线填,免洗的留空。</t>
+          <t xml:space="preserve">     只有 CIP 设备才进 CIP 排程、才算尖峰;非 CIP 设备不填 CIP站。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>6) 带 * 的列必填(表头标黄)。下拉填错词会被拒。</t>
+          <t>5b) 清洗时序 = 3 个动作时长(分钟)× 4 个保持窗(小时)。动作:CIP(全清洗)/ RIP(淋洗在位,层析/UFDF 常以 RIP+SIP 替代罐式 CIP)/ SIP(灭菌)。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>7) 填写顺序:先「站」「房间」→ 再「设备」→ 再「管线」。下游下拉来自上游已录的编码,自动增长。</t>
+          <t xml:space="preserve">     保持窗:DHT(脏停放=变脏后须几小时内开洗)/ RHT(淋洗有效期=RIP 完须几小时内 SIP/被用)/ CHT(洁净有效期=CIP 完须几小时内被用)/ SHT(无菌有效期=SIP 完须几小时内被用)。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     只对要清洗的设备/管线填,不做的留空;管线也可 RIP+SIP(在线灭菌转移线)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6) 带 * 的列必填(表头标黄)。枚举类下拉(清洗方式/洁净级别/类别/起算)填错会被拒;「类型」下拉为建议、可改写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>7) 填写顺序:先「站」「房间」→ 再「设备」→ 再「管线」。下游下拉来自上游已录的编码,自动增长。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>8) 导入按「设施+编码」upsert:已存在则更新,不存在则新增;重复导入不会建重复。</t>
         </is>
@@ -669,7 +690,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="team 编码(只到 team 层级)" type="list" errorStyle="warning">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="team 编码(只到 team 层级)" type="list" errorStyle="warning">
       <formula1>=组织编码</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
@@ -775,7 +796,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="team 编码(只到 team 层级)" type="list" errorStyle="warning">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="team 编码(只到 team 层级)" type="list" errorStyle="warning">
       <formula1>=组织编码</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="请从下拉中选择有效值" type="list" errorStyle="stop">
@@ -792,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -805,9 +826,12 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -858,20 +882,35 @@
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
+          <t>RIP时长(分钟)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
           <t>SIP时长(分钟)</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>DHT(小时)</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>RHT(小时)</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>CHT(小时)</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>SHT(小时)</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -890,7 +929,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>储罐</t>
+          <t>配液罐</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -914,13 +953,16 @@
         <v>90</v>
       </c>
       <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="n">
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>组织留空=随房间</t>
         </is>
@@ -939,7 +981,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>反应器</t>
+          <t>生物反应器</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -962,18 +1004,23 @@
       <c r="I3" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>CIP后SIP</t>
+      <c r="O3" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>CIP后SIP→填SHT</t>
         </is>
       </c>
     </row>
@@ -990,7 +1037,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>反应器</t>
+          <t>生物反应器</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1010,7 +1057,10 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>一次性免CIP,站/时长全留空</t>
         </is>
@@ -1029,7 +1079,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>转移</t>
+          <t>配液罐</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1053,13 +1103,16 @@
         <v>60</v>
       </c>
       <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>母系统:下面挂多个使用点</t>
         </is>
@@ -1078,7 +1131,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>转移/管路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1098,7 +1151,10 @@
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>子设备:房间/组织留空→随上级BUF-SYS</t>
         </is>
@@ -1117,7 +1173,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>层析skid</t>
+          <t>层析 skid</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1137,39 +1193,50 @@
           <t>CIP-2</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="n">
+        <v>40</v>
+      </c>
       <c r="K7" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="L7" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="L7" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>层析不做罐式CIP:RIP+SIP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="请从下拉中选择有效值" type="list" errorStyle="stop">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="默认类型;不够用就在系统「设备类型」里加,这里可直接改写" type="list" errorStyle="warning">
       <formula1>=设备类型</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="请从下拉中选择有效值" type="list" errorStyle="stop">
       <formula1>=清洗方式</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="可选:pou 等使用点挂到母设备/skid;选「设备」里已录的编码,留空=顶层" type="list" errorStyle="warning">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="可选:pou 等使用点挂到母设备/skid;选「设备」里已录的编码,留空=顶层" type="list" errorStyle="warning">
       <formula1>=设备编码</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="选「房间」表里已录的房间编码;留空随上级设备" type="list" errorStyle="warning">
+    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="选「房间」表里已录的房间编码;留空随上级设备" type="list" errorStyle="warning">
       <formula1>=房间编码</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="留空=随房间/上级;否则填 team 编码" type="list" errorStyle="warning">
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="留空=随房间/上级;否则填 team 编码" type="list" errorStyle="warning">
       <formula1>=组织编码</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="仅清洗方式=CIP 时填,选「站」表里已录的站编码" type="list" errorStyle="warning">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="仅清洗方式=CIP 时填,选「站」表里已录的站编码" type="list" errorStyle="warning">
       <formula1>=站编码</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="I2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1183,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1192,9 +1259,13 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1230,15 +1301,35 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>RIP时长(分钟)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>SIP时长(分钟)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>DHT(小时)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>RHT(小时)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>CHT(小时)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>SHT(小时)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1273,13 +1364,17 @@
       <c r="F2" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>示例行</t>
         </is>
@@ -1287,16 +1382,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="选「设备」表里已录的设备编码" type="list" errorStyle="warning">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="选「设备」表里已录的设备编码" type="list" errorStyle="warning">
       <formula1>=设备编码</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="选「设备」表里已录的设备编码" type="list" errorStyle="warning">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="选「设备」表里已录的设备编码" type="list" errorStyle="warning">
       <formula1>=设备编码</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该编码在上游表里还没有,确认无误再继续" promptTitle="提示" prompt="选「站」表里已录的站编码" type="list" errorStyle="warning">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="无效值" error="该值不在当前下拉,确认无误再继续(导入时以系统校验)" promptTitle="提示" prompt="选「站」表里已录的站编码" type="list" errorStyle="warning">
       <formula1>=站编码</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="F2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1440,7 +1535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1478,7 +1573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>反应器</t>
+          <t>生物反应器</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1510,7 +1605,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>层析skid</t>
+          <t>种子反应器</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1542,7 +1637,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>储罐</t>
+          <t>配液罐</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1574,7 +1669,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>超滤skid</t>
+          <t>缓冲液罐</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1601,7 +1696,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>转移</t>
+          <t>培养基罐</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1618,12 +1713,131 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>储液罐</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>设备洁净</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>中间罐</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>移动罐</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>离心机</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>深层过滤器</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>除菌过滤器</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>层析 skid</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>超滤 skid</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>病毒灭活</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>病毒过滤</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>冻干机</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>灌装机</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>称量配制</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>取样</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CIP skid</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SIP skid</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>转移/管路</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>其他</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>设备洁净</t>
         </is>
       </c>
     </row>
